--- a/docs/xlsx/jobs-2026-08-23.xlsx
+++ b/docs/xlsx/jobs-2026-08-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
   <si>
     <t>Title</t>
   </si>
@@ -40,18 +40,126 @@
     <t>Link</t>
   </si>
   <si>
+    <t>(Contractor) Learning Content Instructional Design and LMS Development Services</t>
+  </si>
+  <si>
+    <t>Black Women's Health Imperative</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Health Medicine, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ed250e371cc46d5b83a731440e77923-contractor-learning-content-instructional-design-and-lms-development-services-black-womens-health-imperative-washington</t>
+  </si>
+  <si>
+    <t>Applications &amp; Submissions Operations Supervisor</t>
+  </si>
+  <si>
+    <t>Anthos Home</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3d5a375ae05a4a2b9f10554ad7e69739-applications-submissions-operations-supervisor-anthos-home-new-york</t>
+  </si>
+  <si>
+    <t>Benefits &amp; Financial Literacy Specialist</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1351c0c6a6dd4fdd88128e99aeba9e4e-benefits-financial-literacy-specialist-anthos-home-new-york</t>
+  </si>
+  <si>
+    <t>Client Assessment Manager</t>
+  </si>
+  <si>
+    <t>The Partnership To End Homelessness</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/86b84ceb77e843cd9c2e06c557a775fc-client-assessment-manager-the-partnership-to-end-homelessness-new-york</t>
+  </si>
+  <si>
+    <t>Community / Coalition Organizer - part-time</t>
+  </si>
+  <si>
+    <t>Alliance for Community Services</t>
+  </si>
+  <si>
+    <t>Bloomington, Illinois</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a512ffeff9347bda68d2e911924150b-community-coalition-organizer-part-time-alliance-for-community-services-bloomington</t>
+  </si>
+  <si>
+    <t>Deputy Legal Director</t>
+  </si>
+  <si>
+    <t>The New York Immigration Coalition</t>
+  </si>
+  <si>
+    <t>USD 133000.00 - 133000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c4962fedc34432588fea5fb08dad762-deputy-legal-director-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Refuge House, Inc.</t>
+  </si>
+  <si>
+    <t>Tallahassee, Florida</t>
+  </si>
+  <si>
+    <t>Sexual Abuse Human Trafficking, Victim Support, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1f7841d4ad043eeb7ad807a9161abda-executive-director-refuge-house-inc-tallahassee</t>
+  </si>
+  <si>
     <t>Finance Coordinator</t>
   </si>
   <si>
     <t>Grand Street Settlement</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 70000.00 - 80000.00/year</t>
   </si>
   <si>
@@ -59,6 +167,93 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/494aafafc73949d792dbe00bed0da0e0-finance-coordinator-grand-street-settlement-new-york</t>
+  </si>
+  <si>
+    <t>Legal Assistant</t>
+  </si>
+  <si>
+    <t>USD 59100.00 - 59100.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bb378730e2d94207892a58f8727cd137-legal-assistant-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
+    <t>Managing Attorney</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7bee217efd0f4997b1bafa22ffb60586-managing-attorney-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
+    <t>National Organizer</t>
+  </si>
+  <si>
+    <t>The Transgender Law Center</t>
+  </si>
+  <si>
+    <t>USD 98300.00 - 103000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/81ffb0d7929a4b55b7af9af1a8ba8132-national-organizer-the-transgender-law-center-oakland</t>
+  </si>
+  <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>USD 75800.00 - 75800.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bde8a32a56db466d834f648d96a9b8f9-paralegal-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
+    <t>Project Manager (Program Management Department) [based in Seoul]</t>
+  </si>
+  <si>
+    <t>International Vaccine Institute</t>
+  </si>
+  <si>
+    <t>Seoul, Seoul, KR</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c349a53e79654162839f5c0f8daa82da-project-manager-program-management-department-based-in-seoul-international-vaccine-institute-seoul</t>
+  </si>
+  <si>
+    <t>Senior Paralegal</t>
+  </si>
+  <si>
+    <t>USD 81000.00 - 81000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d03a9c6567b4f7ab604dbdf1e3f6e63-senior-paralegal-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
+    <t>Senior Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f737a93e2c394a8a9d3b365d22113fb2-senior-staff-attorney-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 95481.00 - 95481.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/12f00b809d8a4c8f90a9bdff8d9a9b7e-staff-attorney-the-new-york-immigration-coalition-new-york</t>
   </si>
 </sst>
 </file>
@@ -540,7 +735,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -602,10 +797,370 @@
         <v>14</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-23.xlsx
+++ b/docs/xlsx/jobs-2026-08-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="132">
   <si>
     <t>Title</t>
   </si>
@@ -91,6 +91,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/1351c0c6a6dd4fdd88128e99aeba9e4e-benefits-financial-literacy-specialist-anthos-home-new-york</t>
   </si>
   <si>
+    <t>Chief of Staff [Strategic Operations], Delhi</t>
+  </si>
+  <si>
+    <t>Ground Zero</t>
+  </si>
+  <si>
+    <t>Delhi, Delhi, IN</t>
+  </si>
+  <si>
+    <t>INR 1500000.00 - 2000000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e1f47c22b9f46b5828ea8068f6da4d6-chief-of-staff-strategic-operations-delhi-ground-zero-delhi</t>
+  </si>
+  <si>
     <t>Client Assessment Manager</t>
   </si>
   <si>
@@ -139,6 +157,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/8c4962fedc34432588fea5fb08dad762-deputy-legal-director-the-new-york-immigration-coalition-new-york</t>
   </si>
   <si>
+    <t>Europe Programme Officer</t>
+  </si>
+  <si>
+    <t>International Detention Coalition</t>
+  </si>
+  <si>
+    <t>Remote (ES)</t>
+  </si>
+  <si>
+    <t>EUR 35000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd6ca393b1a14b0e8978fb3284bb5ac1-europe-programme-officer-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
+    <t>Remote (NL)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f058ed73a4e544efa43df6635ad7fa5d-europe-programme-officer-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
+    <t>Remote (DE)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9afb562962b147c9bc52393179eeba9d-europe-programme-officer-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
+    <t>Remote (GB)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/881897177b5d4c9394efccfd1da61901-europe-programme-officer-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -169,6 +223,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/494aafafc73949d792dbe00bed0da0e0-finance-coordinator-grand-street-settlement-new-york</t>
   </si>
   <si>
+    <t>Fundraising Lead, Bangalore</t>
+  </si>
+  <si>
+    <t>Bangalore, Bangalore, IN</t>
+  </si>
+  <si>
+    <t>INR 2000000.00 - 2500000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/56d79906ea53400f912aa5bfeec0db2e-fundraising-lead-bangalore-ground-zero-bangalore</t>
+  </si>
+  <si>
+    <t>Head of Fundraising &amp; Partnerships, Delhi</t>
+  </si>
+  <si>
+    <t>New Delhi, New Delhi, IN</t>
+  </si>
+  <si>
+    <t>INR 1800000.00 - 1900000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1feec8c4a37c4b0087bed3cd1a232509-head-of-fundraising-partnerships-delhi-ground-zero-new-delhi</t>
+  </si>
+  <si>
+    <t>Immigrants’ Rights Staff Attorney or Senior Attorney Position</t>
+  </si>
+  <si>
+    <t>TakeRoot Justice</t>
+  </si>
+  <si>
+    <t>USD 83490.00 - 96550.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dee2ac33f04c4dda8035e340d3b27e8d-immigrants-rights-staff-attorney-or-senior-attorney-position-takeroot-justice-new-york</t>
+  </si>
+  <si>
     <t>Legal Assistant</t>
   </si>
   <si>
@@ -178,6 +271,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/bb378730e2d94207892a58f8727cd137-legal-assistant-the-new-york-immigration-coalition-new-york</t>
   </si>
   <si>
+    <t>Manager - Government Partnerships, Mumbai</t>
+  </si>
+  <si>
+    <t>Mumbai, Mumbai, IN</t>
+  </si>
+  <si>
+    <t>INR 1000000.00 - 1500000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42964b55df1d4ac88063b5bf8563f415-manager-government-partnerships-mumbai-ground-zero-mumbai</t>
+  </si>
+  <si>
     <t>Managing Attorney</t>
   </si>
   <si>
@@ -211,6 +316,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/bde8a32a56db466d834f648d96a9b8f9-paralegal-the-new-york-immigration-coalition-new-york</t>
   </si>
   <si>
+    <t>Programme Coordinator (Education), Sangareddy ,Telangana</t>
+  </si>
+  <si>
+    <t>Sangareddy, Sangareddy, IN</t>
+  </si>
+  <si>
+    <t>INR 400000.00 - 420000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/628e646407724f4f936f292f21279550-programme-coordinator-education-sangareddy-telangana-ground-zero-sangareddy</t>
+  </si>
+  <si>
+    <t>Programme Director (Education), Sukma, Bastar, Chhattisgarh</t>
+  </si>
+  <si>
+    <t>Bastar, Bastar, IN</t>
+  </si>
+  <si>
+    <t>INR 1000000.00 - 1200000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3dba0b82ced443bb8d736e58f6fc18b8-programme-director-education-sukma-bastar-chhattisgarh-ground-zero-bastar</t>
+  </si>
+  <si>
     <t>Project Manager (Program Management Department) [based in Seoul]</t>
   </si>
   <si>
@@ -226,6 +355,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/c349a53e79654162839f5c0f8daa82da-project-manager-program-management-department-based-in-seoul-international-vaccine-institute-seoul</t>
   </si>
   <si>
+    <t>Senior Manager - Monitoring, Evaluation and Learning, Delhi</t>
+  </si>
+  <si>
+    <t>INR 1200000.00 - 2000000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d05608c7ea0542bc884a5cbbdfe46201-senior-manager-monitoring-evaluation-and-learning-delhi-ground-zero-delhi</t>
+  </si>
+  <si>
+    <t>Senior Manager - Monitoring, Evaluation and Learning, Pune</t>
+  </si>
+  <si>
+    <t>Pune, Pune, IN</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bea2f12e066b4991a18441412ae6009c-senior-manager-monitoring-evaluation-and-learning-pune-ground-zero-pune</t>
+  </si>
+  <si>
     <t>Senior Paralegal</t>
   </si>
   <si>
@@ -254,6 +401,15 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/12f00b809d8a4c8f90a9bdff8d9a9b7e-staff-attorney-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
+    <t>Team Lead- Program Management, Pune/ Bhopal</t>
+  </si>
+  <si>
+    <t>INR 1300000.00 - 1400000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49618429e97749b7840c15c6d01f2baf-team-lead-program-management-pune-bhopal-ground-zero-pune</t>
   </si>
 </sst>
 </file>
@@ -735,7 +891,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -857,231 +1013,231 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" t="s">
         <v>51</v>
       </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
         <v>62</v>
       </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="H13" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="F13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
         <v>65</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
         <v>66</v>
       </c>
-      <c r="C14" t="s">
+      <c r="F14" t="s">
         <v>67</v>
       </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="H14" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
         <v>70</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>17</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -1090,7 +1246,7 @@
         <v>71</v>
       </c>
       <c r="F15" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>72</v>
@@ -1101,19 +1257,19 @@
         <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>76</v>
@@ -1124,7 +1280,7 @@
         <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
@@ -1133,13 +1289,335 @@
         <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>111</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>114</v>
+      </c>
+      <c r="F27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>120</v>
+      </c>
+      <c r="F28" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>123</v>
+      </c>
+      <c r="F29" t="s">
+        <v>124</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F30" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>129</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>130</v>
+      </c>
+      <c r="F31" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1161,6 +1639,20 @@
     <hyperlink ref="H15" r:id="rId14"/>
     <hyperlink ref="H16" r:id="rId15"/>
     <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
